--- a/docs/deveconomics/DigitalSecretary-DevEconomics.xlsx
+++ b/docs/deveconomics/DigitalSecretary-DevEconomics.xlsx
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -953,12 +953,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Requirements</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Brainstorm uses; draft email-intelligence requirements (Groups A-K)</t>
+          <t>Review project status after 4 months idle: CLAUDE.md, contract, a reference feature, docgen gates, tests, build.ps1</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>9000</v>
+        <v>46000</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>BA/product doc</t>
+          <t>one-time re-orientation</t>
         </is>
       </c>
     </row>
@@ -1002,41 +1002,39 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Requirements</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Add timeline / documents / progress / HTML-report requirements</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Verify dotnet 9 SDK + python/openpyxl</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Bash</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>4000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -1047,12 +1045,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Requirements</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Read CLAUDE.md, contract, EmailDownloader, build.ps1, docgen, tests (~20 reads)</t>
+          <t>Draft the canonical spec: 19 DDF requirements + 15 traceability rows from the user's brief</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1062,7 +1060,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1071,13 +1069,13 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40000</v>
+        <v>11000</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0.45</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -1086,7 +1084,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>one-time pattern learning</t>
+          <t>reused verbatim by 2 subagents</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1094,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Read ADDING_A_FEATURE, check_docs, build_excel_docs, coverage.runsettings</t>
+          <t>Author the pure core: checksum entry/list/index, MD5 hasher, byte comparer, pause gate, hex, sizes</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1111,7 +1109,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1120,13 +1118,13 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1133,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>quality gates</t>
+          <t>logic kept out of the UI</t>
         </is>
       </c>
     </row>
@@ -1145,39 +1143,41 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Verify dotnet/python/nuget/git + MimeKit cache</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Author ScanEngine (incremental walk, autosave, prune) + DuplicateAnalyzer (groups, keeper policy)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Bash</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>11000</v>
+      </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.3</v>
+        <v>7</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Build P1</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Author models + MailText + EmailParser + ArchiveScanner</t>
+          <t>Author DeleteEngine + deleters + report text + settings store + existing-list prompt</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>MimeKit + .txt</t>
+          <t>guarded deletion</t>
         </is>
       </c>
     </row>
@@ -1237,46 +1237,44 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Build P1</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Compile parsing slice</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Author the WinForms view (folder, options, commands, progress, duplicate grid, log)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>dotnet build</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>9000</v>
+      </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.15</v>
+        <v>6</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8.7s</t>
-        </is>
-      </c>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1284,12 +1282,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Build P1</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Author 9 analyzer classes (dedupe/contacts/identity/signature/metrics/graph/topics/timeline/classify)</t>
+          <t>Clear 4 CA1859 warnings; match button labels to the manual; confirm-dialog default; log-pane layout</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1299,7 +1297,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1308,20 +1306,24 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>layout fault seen in the screenshot</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1329,44 +1331,46 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Build P1</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Fix nullable + CA1859 warnings</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Compile the feature (0 warnings)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>dotnet build</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1500</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>29s then 3s</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1374,48 +1378,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Build P1</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Author exporters + HTML report generator + pipeline + settings + UI + module</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Add project to sln + unit-test reference + coverage exclusion</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>dotnet sln / python</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>16000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>report has embedded CSS/JS</t>
-        </is>
-      </c>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1423,42 +1421,48 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Build P1</t>
+          <t>Docs (agent)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Compile full feature (0 warnings)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Subagent in parallel: requirements doc, user guide, README row, Pages card</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>dotnet build</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>83554</v>
+      </c>
       <c r="H12" s="4" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>tokens + duration from the harness</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1466,12 +1470,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tests P1</t>
+          <t>Docgen (agent)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Author 14 unit-test files + fixtures</t>
+          <t>Subagent in parallel: 19 req + 15 trace rows, id regex, manual section, DocShots seed, regenerate xlsx</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1490,20 +1494,24 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>10000</v>
+        <v>93143</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>tokens + duration from the harness</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1511,42 +1519,48 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Tests P1</t>
+          <t>Tests (agent)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Add feature reference to unit-test project</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Subagent: 12 unit-test files (144 tests) + QA id list, iterated to green</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>dotnet add reference</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>171867</v>
+      </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.1</v>
+        <v>14.3</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>tokens + duration from the harness</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1554,46 +1568,44 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Tests P1</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Run unit tests (121)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Author FEATURE.md (design decisions + file map)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>dotnet test</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>4500</v>
+      </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.12</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>7s</t>
-        </is>
-      </c>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1601,12 +1613,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Author FEATURE.md + user-guide doc</t>
+          <t>Read back the subagents' docs, manual section and tests; align UI labels with the guide</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1616,7 +1628,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1625,20 +1637,24 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>delegated work is verified, not trusted</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1646,12 +1662,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Docgen</t>
+          <t>Bugfix</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Edit build_excel_docs (37 reqs + 16 trace) + check_docs EI id regex</t>
+          <t>Diagnose + fix prune-on-cancel (S2) found by the test agent; add the regression test</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1670,10 +1686,10 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>4</v>
@@ -1683,7 +1699,11 @@
           <t>estimate</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>BUG-1; see KNOWN pitfalls</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1691,12 +1711,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Docgen</t>
+          <t>Bugfix</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Regenerate xlsx + run check_docs + secret scan</t>
+          <t>Prove the regression test fails before the fix and passes after</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1706,7 +1726,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>dotnet build/test</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1719,14 +1739,18 @@
         <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>revert -&gt; fail -&gt; restore -&gt; pass</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1734,12 +1758,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Full quality gate</t>
+          <t>Solution builds + unit-test runs (316 tests)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1749,7 +1773,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>build.ps1 -All</t>
+          <t>dotnet build/test</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1762,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1795,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>PASS, 92%</t>
+          <t>0.7s per run</t>
         </is>
       </c>
     </row>
@@ -1781,44 +1805,46 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Docgen</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Append DEVELOPMENT_JOURNAL phase</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Regenerate DocShots screenshots + HTML user manual (twice, after the layout fix)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>dotnet run + powershell</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>2500</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1.5</v>
+        <v>0.65</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>cleanliness check PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1826,46 +1852,44 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Append</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Add AnalysisMode + ScanAndParse/AnalyzeCore refactor (EI-I4)</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Full quality gate</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>build.ps1 -All</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>7000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>5</v>
+        <v>0.63</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>consolidate archives</t>
+          <t>PASS, 92.2%, 316+21 tests</t>
         </is>
       </c>
     </row>
@@ -1875,44 +1899,46 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Append</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Wire Append checkbox into the UI</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Storage report</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>node storage-report.mjs</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>docs/pm/STORAGE.md</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1920,12 +1946,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Append</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Author MessageStore + append/overwrite tests</t>
+          <t>Journal phase, CHANGELOG, DevEconomics, PM trackers (TASKS/WORKLOG/STORAGE)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1935,7 +1961,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Write/Edit</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1944,20 +1970,24 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3500</v>
+        <v>11000</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>this release entry</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1965,12 +1995,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Append</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Run tests (125)</t>
+          <t>Stage + commit (pre-commit gate)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1980,7 +2010,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>dotnet test</t>
+          <t>git commit</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1993,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2003,727 +2033,30 @@
       <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Append</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Register EI-I4 + regenerate + gate</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>python/build.ps1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Build P3</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Author SentimentLexicon + ToneAnalyzer + LifeDataExtractor + DocumentLibrary + model fields</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Write</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>E2, F1-F4, F7</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Build P3</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Wire pipeline + CSV exporters + JSON + 2 HTML tabs</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Edit</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Build P3</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Author 3 analyzer test files</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Write</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Build P3</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Run tests (147)</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>dotnet test</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Build P3</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Register E2/F + regenerate + gate</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>python/build.ps1</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Build P4</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Author XlsxWriter (dependency-free OOXML) + WorkbookExporter + wire pipeline</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Write</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>native .xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Build P4</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Hoist header arrays (CA1861)</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Edit</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Build P4</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Author XlsxWriter tests</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Write</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Build P4</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Validate .xlsx with openpyxl (throwaway runner)</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>dotnet run + python</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>3 sheets, typed numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Build P4</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Register EI-H7 + regenerate + gate</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>python/build.ps1</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>PASS, 91.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Fix test fixtures to example.com (secret gate) + stage</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Bash/Edit</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>74 leaks -&gt; 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Commit feature + xlsx (pre-commit gate x2)</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>git commit</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>84d97dd, 3562b3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Push main to origin</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>B+C - Local+net ($0)</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>git push</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>DevEconomics + CHANGELOG + cut release</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Write/Edit</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>this release entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>TOTAL (direct, sum of activities)</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="7">
-        <f>SUM(G2:G39)</f>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="7">
+        <f>SUM(G2:G24)</f>
         <v/>
       </c>
-      <c r="H40" s="8">
-        <f>SUM(H2:H39)</f>
+      <c r="H25" s="8">
+        <f>SUM(H2:H24)</f>
         <v/>
       </c>
-      <c r="I40" s="9">
-        <f>SUM(I2:I39)</f>
+      <c r="I25" s="9">
+        <f>SUM(I2:I24)</f>
         <v/>
       </c>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
@@ -2856,12 +2189,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prior releases (host + 6 features + quality/docs/CI/release infra, through v2.1.0)</t>
+          <t>Prior releases (host + 7 features + quality/docs/CI/release infra, through v2.2.0)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19..22</t>
+          <t>2026-06-19..23</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2873,15 +2206,15 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n">
-        <v>2.73</v>
+        <v>5.23</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>2121000</v>
+        <v>2303700</v>
       </c>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n">
-        <v>50.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4">
@@ -2890,57 +2223,57 @@
       </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n">
-        <v>768</v>
+        <v>867.7</v>
       </c>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="4" t="n">
-        <v>18.5</v>
+        <v>13.69</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>ROUGH estimate: phases 1-17 predate DevEconomics tracking; includes the tracked Gmail/Drive release (v2.1.0, ~$5.50).</t>
+          <t>Phases 1-17 predate DevEconomics tracking (rough estimate); includes the tracked v2.1.0 and v2.2.0 releases.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Email Intelligence</t>
+          <t>DeDupe Files</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Opus 4.8</t>
+          <t>Opus 5</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>182700</v>
+        <v>485064</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>5.1</v>
+        <v>7.74</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>21.1</v>
+        <v>16.74</v>
       </c>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4">
@@ -2948,14 +2281,14 @@
         <v/>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5.12</v>
+        <v>3.83</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>99.72</v>
+        <v>87.53</v>
       </c>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="4" t="n">
-        <v>8.44</v>
+        <v>7.75</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -3144,7 +2477,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>38 activities (23 LLM / 15 local|remote); ~$21.1 est; ~99.72 min est (~5.12 min measured local compute).</t>
+          <t>23 activities (14 LLM / 9 local|remote); ~$16.74 est; ~87.53 min est (~3.83 min measured local compute).</t>
         </is>
       </c>
     </row>
@@ -3156,7 +2489,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>~5.23 prod KLOC; ~$71.6 est; ~14.5 h est. Foundation portion is a ROUGH pre-tracking estimate.</t>
+          <t>~7.39 prod KLOC; ~$88.34 est; ~15.9 h est. Foundation portion is a ROUGH pre-tracking estimate.</t>
         </is>
       </c>
     </row>

--- a/docs/deveconomics/DigitalSecretary-DevEconomics.xlsx
+++ b/docs/deveconomics/DigitalSecretary-DevEconomics.xlsx
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Review project status after 4 months idle: CLAUDE.md, contract, a reference feature, docgen gates, tests, build.ps1</t>
+          <t>Read WORKLOG/TASKS/git state; summarise latest updates + pending items</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46000</v>
+        <v>30000</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>one-time re-orientation</t>
+          <t>session start</t>
         </is>
       </c>
     </row>
@@ -1002,22 +1002,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Verify dotnet 9 SDK + python/openpyxl</t>
+          <t>Resolve OWN-1/OWN-2: verify release zips on GitHub, prune old build output, move stray decks</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>B - Local ($0)</t>
+          <t>B+C - Local+net ($0)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bash</t>
+          <t>bash / gh</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1030,14 +1030,18 @@
         <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>681.5 MB -&gt; 309.2 MB</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1045,12 +1049,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Requirements</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Draft the canonical spec: 19 DDF requirements + 15 traceability rows from the user's brief</t>
+          <t>Deep strategy: Storage Studio (space map, similar pictures, similar videos), phasing, risks</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1069,13 +1073,13 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0.45</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -1084,7 +1088,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>reused verbatim by 2 subagents</t>
+          <t>owner chose phase 1 first</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1098,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Author the pure core: checksum entry/list/index, MD5 hasher, byte comparer, pause gate, hex, sizes</t>
+          <t>Study the add-a-feature recipe, DeDupe Files as a model, docgen tables, DocShots, QA harness</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1109,7 +1113,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1118,10 +1122,10 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13000</v>
+        <v>40000</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>8</v>
@@ -1131,11 +1135,7 @@
           <t>estimate</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>logic kept out of the UI</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1143,44 +1143,46 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Author ScanEngine (incremental walk, autosave, prune) + DuplicateAnalyzer (groups, keeper policy)</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Baseline full quality gate before any change</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>build.ps1 -All</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>11000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>316 + 21 green</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1193,7 +1195,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Author DeleteEngine + deleters + report text + settings store + existing-list prompt</t>
+          <t>Author the pure engine: SpaceNode, SpaceScanner, SpaceAnalyzer, CleanupFinder, TreemapLayout (squarified), snapshot/growth/store, report, settings, palette</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1212,13 +1214,13 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.42</v>
+        <v>1.05</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1229,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>guarded deletion</t>
+          <t>logic kept out of the UI</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1244,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Author the WinForms view (folder, options, commands, progress, duplicate grid, log)</t>
+          <t>Author the UI: TreemapControl, BarChartControl, StorageStudioControl</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1261,13 +1263,13 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1287,7 +1289,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Clear 4 CA1859 warnings; match button labels to the manual; confirm-dialog default; log-pane layout</t>
+          <t>Fix 4 WFO1000 + 2 CA warnings (designer serialization, return type, naming)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1306,24 +1308,20 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>layout fault seen in the screenshot</t>
-        </is>
-      </c>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1336,7 +1334,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Compile the feature (0 warnings)</t>
+          <t>Add project to sln + test reference; compile (0 warnings)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1346,7 +1344,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>dotnet build</t>
+          <t>dotnet sln / build</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1359,18 +1357,14 @@
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>29s then 3s</t>
-        </is>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1378,42 +1372,48 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Add project to sln + unit-test reference + coverage exclusion</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Author 14 unit-test files (89 test methods) incl. the scan -&gt; snapshot -&gt; rescan integration test</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>dotnet sln / python</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>26000</v>
+      </c>
       <c r="H11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.2</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>green on first full run</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Docs (agent)</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Subagent in parallel: requirements doc, user guide, README row, Pages card</t>
+          <t>QA test (real plugin, sample tree, simulated click) + DocShots sample hook + SampleSpaceTree</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1445,22 +1445,22 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>83554</v>
+        <v>8000</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.95</v>
+        <v>0.3</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>tokens + duration from the harness</t>
+          <t>no real path in any screenshot</t>
         </is>
       </c>
     </row>
@@ -1470,37 +1470,35 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Docgen (agent)</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Subagent in parallel: 19 req + 15 trace rows, id regex, manual section, DocShots seed, regenerate xlsx</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Unit + QA runs</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>dotnet test</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>93143</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
       <c r="H13" s="4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1509,7 +1507,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>tokens + duration from the harness</t>
+          <t>444 unit + 24 QA</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1517,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Tests (agent)</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Subagent: 12 unit-test files (144 tests) + QA id list, iterated to green</t>
+          <t>Read the rendered screenshot; fix map height, '&amp;' mnemonic, bar width</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1534,7 +1532,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Read/Edit</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1543,22 +1541,22 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>171867</v>
+        <v>4000</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.95</v>
+        <v>0.12</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>14.3</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>tokens + duration from the harness</t>
+          <t>seen in the screenshot</t>
         </is>
       </c>
     </row>
@@ -1568,41 +1566,39 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Docgen</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Author FEATURE.md (design decisions + file map)</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Regenerate DocShots screenshots (twice)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>dotnet run</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>4500</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -1613,12 +1609,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Read back the subagents' docs, manual section and tests; align UI labels with the guide</t>
+          <t>FEATURE.md, requirement doc (SST-1..17), user guide, manual section, hubs, README row, Pages card</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1628,7 +1624,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1637,13 +1633,13 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>12000</v>
+        <v>22000</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3</v>
+        <v>0.85</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1652,7 +1648,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>delegated work is verified, not trusted</t>
+          <t>also fixed hub drift (BUG-1)</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1658,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Bugfix</t>
+          <t>Docgen</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Diagnose + fix prune-on-cancel (S2) found by the test agent; add the regression test</t>
+          <t>17 requirement + 13 traceability rows, SST id in check_docs regex</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1677,7 +1673,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1686,24 +1682,20 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>BUG-1; see KNOWN pitfalls</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1711,12 +1703,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Bugfix</t>
+          <t>Docgen</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Prove the regression test fails before the fix and passes after</t>
+          <t>Regenerate requirements/traceability xlsx + HTML user manual; docs check</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1726,7 +1718,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>dotnet build/test</t>
+          <t>python + powershell</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1739,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1748,7 +1740,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>revert -&gt; fail -&gt; restore -&gt; pass</t>
+          <t>cleanliness check PASSED</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1750,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Solution builds + unit-test runs (316 tests)</t>
+          <t>Full quality gate</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1773,7 +1765,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>dotnet build/test</t>
+          <t>build.ps1 -All</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1786,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1795,7 +1787,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0.7s per run</t>
+          <t>PASS, 468 tests</t>
         </is>
       </c>
     </row>
@@ -1805,44 +1797,46 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Docgen</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Regenerate DocShots screenshots + HTML user manual (twice, after the layout fix)</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>CHANGELOG 2.4.0, journal phase 23, DevEconomics, PM trackers</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>dotnet run + powershell</t>
+          <t>Write/Edit</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="H20" s="4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.65</v>
+        <v>8</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>cleanliness check PASSED</t>
+          <t>this release entry</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1851,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Full quality gate</t>
+          <t>Storage report</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1867,7 +1861,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>build.ps1 -All</t>
+          <t>node storage-report.mjs</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1880,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.63</v>
+        <v>0.2</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1889,174 +1883,35 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>PASS, 92.2%, 316+21 tests</t>
+          <t>docs/pm/STORAGE.md</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Storage report</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>node storage-report.mjs</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>docs/pm/STORAGE.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Journal phase, CHANGELOG, DevEconomics, PM trackers (TASKS/WORKLOG/STORAGE)</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Write/Edit</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>this release entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Stage + commit (pre-commit gate)</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>git commit</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>TOTAL (direct, sum of activities)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="7">
-        <f>SUM(G2:G24)</f>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="7">
+        <f>SUM(G2:G21)</f>
         <v/>
       </c>
-      <c r="H25" s="8">
-        <f>SUM(H2:H24)</f>
+      <c r="H22" s="8">
+        <f>SUM(H2:H21)</f>
         <v/>
       </c>
-      <c r="I25" s="9">
-        <f>SUM(I2:I24)</f>
+      <c r="I22" s="9">
+        <f>SUM(I2:I21)</f>
         <v/>
       </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
@@ -2189,12 +2044,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prior releases (host + 7 features + quality/docs/CI/release infra, through v2.2.0)</t>
+          <t>Prior releases (host + 8 features + quality/docs/CI/release infra, through v2.3.0)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19..23</t>
+          <t>2026-06-19..10-28</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2206,15 +2061,15 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n">
-        <v>5.23</v>
+        <v>7.39</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>2303700</v>
+        <v>2788764</v>
       </c>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>88.34</v>
       </c>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4">
@@ -2223,57 +2078,57 @@
       </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n">
-        <v>867.7</v>
+        <v>955.2</v>
       </c>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="4" t="n">
-        <v>13.69</v>
+        <v>11.95</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Phases 1-17 predate DevEconomics tracking (rough estimate); includes the tracked v2.1.0 and v2.2.0 releases.</t>
+          <t>Phases 1-17 predate DevEconomics tracking (rough estimate); includes the tracked v2.1.0, v2.2.0 and v2.3.0 releases.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DeDupe Files</t>
+          <t>Storage Studio (Space Map)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Opus 5</t>
+          <t>Opus 5.5</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>485064</v>
+        <v>207000</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>7.74</v>
+        <v>6.05</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>16.74</v>
+        <v>18.05</v>
       </c>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4">
@@ -2281,18 +2136,18 @@
         <v/>
       </c>
       <c r="N3" s="2" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>87.53</v>
+        <v>100.1</v>
       </c>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="4" t="n">
-        <v>7.75</v>
+        <v>7.92</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Estimate; reconcile ACTUAL via /cost. Spans 3 increments (foundation+report, append, tone/life-data/docs, xlsx).</t>
+          <t>Estimate; reconcile ACTUAL via /cost. Phase 1 of Storage Studio (space map); single session.</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2332,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>23 activities (14 LLM / 9 local|remote); ~$16.74 est; ~87.53 min est (~3.83 min measured local compute).</t>
+          <t>20 activities (12 LLM / 8 local|remote); ~$18.05 est; ~100.1 min est (~4.1 min measured local compute).</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2344,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>~7.39 prod KLOC; ~$88.34 est; ~15.9 h est. Foundation portion is a ROUGH pre-tracking estimate.</t>
+          <t>~9.67 prod KLOC; ~$106.39 est; ~17.6 h est. Foundation portion is a ROUGH pre-tracking estimate.</t>
         </is>
       </c>
     </row>

--- a/docs/deveconomics/DigitalSecretary-DevEconomics.xlsx
+++ b/docs/deveconomics/DigitalSecretary-DevEconomics.xlsx
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Read WORKLOG/TASKS/git state; summarise latest updates + pending items</t>
+          <t>Check repo + CI after v2.4.0; frame the four design decisions for the owner</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Read/Ask</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>session start</t>
+          <t>owner chose: separate plugin, review folder, all match kinds, Windows codecs</t>
         </is>
       </c>
     </row>
@@ -1002,46 +1002,44 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Resolve OWN-1/OWN-2: verify release zips on GitHub, prune old build output, move stray decks</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>B+C - Local+net ($0)</t>
+          <t>Author the pure engine: GrayImage (resize, 8 transforms, sharpness), ImageHasher (pHash DCT + dHash), SimilarityFinder (tiers, star grouping), KeeperRanking</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>bash / gh</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>22000</v>
+      </c>
       <c r="H3" s="4" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>681.5 MB -&gt; 309.2 MB</t>
-        </is>
-      </c>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1049,12 +1047,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Deep strategy: Storage Studio (space map, similar pictures, similar videos), phasing, risks</t>
+          <t>Author I/O edges: Shell thumbnail COM interop + GDI+ fallback, EXIF date/sub-seconds/rotation, cache (gzip), scanner (bounded parallel), ReviewMover (move/recycle/undo), FileBytes</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1073,24 +1071,20 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>owner chose phase 1 first</t>
-        </is>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1098,12 +1092,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Study the add-a-feature recipe, DeDupe Files as a model, docgen tables, DocShots, QA harness</t>
+          <t>Author the review UI: PictureCardControl + SimilarPicturesControl; settings, report, sample set</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1113,7 +1107,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1122,13 +1116,13 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40000</v>
+        <v>16000</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -1143,46 +1137,44 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Baseline full quality gate before any change</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Rename Orientation -&gt; PictureOrientation (WinForms name clash); add project to sln + tests</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>build.ps1 -All</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>316 + 21 green</t>
-        </is>
-      </c>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1195,43 +1187,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Author the pure engine: SpaceNode, SpaceScanner, SpaceAnalyzer, CleanupFinder, TreemapLayout (squarified), snapshot/growth/store, report, settings, palette</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Compile the feature (0 warnings)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>dotnet build</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>28000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>logic kept out of the UI</t>
-        </is>
-      </c>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1239,12 +1225,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Calibrate</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Author the UI: TreemapControl, BarChartControl, StorageStudioControl</t>
+          <t>Probe: measure pHash/dHash distances for resize, JPEG, brightness, crop, turns, bursts, unrelated scenes</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1263,20 +1249,24 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>16000</v>
+        <v>5000</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>thresholds set from data</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1284,41 +1274,39 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Calibrate</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Fix 4 WFO1000 + 2 CA warnings (designer serialization, return type, naming)</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Run the probe</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>dotnet test</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1329,39 +1317,41 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Add project to sln + test reference; compile (0 warnings)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Author 12 unit-test files incl. the scan -&gt; group -&gt; move -&gt; rescan -&gt; undo integration test</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>dotnet sln / build</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.6</v>
+        <v>16</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -1372,12 +1362,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Bugfix</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Author 14 unit-test files (89 test methods) incl. the scan -&gt; snapshot -&gt; rescan integration test</t>
+          <t>Fix the int.MaxValue overflow (no pair ever matched), sample capture times, burst bonus on mtime, as-is-only Similar, test inputs</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1387,7 +1377,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1396,13 +1386,13 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>26000</v>
+        <v>12000</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1401,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>green on first full run</t>
+          <t>found by the tests before release</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1411,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>QA test (real plugin, sample tree, simulated click) + DocShots sample hook + SampleSpaceTree</t>
+          <t>Render two near-matching generated scenes and judge them by eye</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1436,7 +1426,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1445,13 +1435,13 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1450,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>no real path in any screenshot</t>
+          <t>they do look alike - test, not code, was wrong</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1507,7 +1497,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>444 unit + 24 QA</t>
+          <t>584 unit + 27 QA</t>
         </is>
       </c>
     </row>
@@ -1517,46 +1507,44 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Read the rendered screenshot; fix map height, '&amp;' mnemonic, bar width</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>A stray `cat` blocked a shell for 5 minutes until stopped</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Read/Edit</t>
+          <t>bash</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>4000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>seen in the screenshot</t>
+          <t>waste - see journal pitfall</t>
         </is>
       </c>
     </row>
@@ -1566,42 +1554,48 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Docgen</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Regenerate DocShots screenshots (twice)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>QA test (real plugin, sample set, simulated click) + DocShots hook; fix DocShots cropping the bottom of every view</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>dotnet run</t>
+          <t>Write/Edit</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>9000</v>
+      </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>BUG-3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1609,48 +1603,42 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Docgen</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>FEATURE.md, requirement doc (SST-1..17), user guide, manual section, hubs, README row, Pages card</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Regenerate DocShots screenshots (three times)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>dotnet run</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>22000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>12</v>
+        <v>1.2</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>also fixed hub drift (BUG-1)</t>
-        </is>
-      </c>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1658,12 +1646,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Docgen</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17 requirement + 13 traceability rows, SST id in check_docs regex</t>
+          <t>FEATURE.md, requirement doc (SIM-1..18), user guide, manual section, hubs, README row, Pages card</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1682,13 +1670,13 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>9000</v>
+        <v>22000</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.35</v>
+        <v>0.85</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1708,41 +1696,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Regenerate requirements/traceability xlsx + HTML user manual; docs check</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>18 requirement + 13 traceability rows, SIM id in check_docs regex</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>python + powershell</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>8000</v>
+      </c>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>cleanliness check PASSED</t>
-        </is>
-      </c>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1750,12 +1736,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Docgen</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Full quality gate</t>
+          <t>Regenerate requirements/traceability xlsx + HTML user manual; docs check</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1765,7 +1751,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>build.ps1 -All</t>
+          <t>python + powershell</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1778,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1787,7 +1773,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>PASS, 468 tests</t>
+          <t>cleanliness check PASSED</t>
         </is>
       </c>
     </row>
@@ -1797,46 +1783,44 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CHANGELOG 2.4.0, journal phase 23, DevEconomics, PM trackers</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Full quality gate</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Write/Edit</t>
+          <t>build.ps1 -All</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>10000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>this release entry</t>
+          <t>PASS, 611 tests, 94.2%</t>
         </is>
       </c>
     </row>
@@ -1846,72 +1830,121 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>CHANGELOG 2.5.0, journal phase 24, DevEconomics, PM trackers</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Write/Edit</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>this release entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Storage report</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>B - Local ($0)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>node storage-report.mjs</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="4" t="n">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>docs/pm/STORAGE.md</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>TOTAL (direct, sum of activities)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="7">
-        <f>SUM(G2:G21)</f>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="7">
+        <f>SUM(G2:G22)</f>
         <v/>
       </c>
-      <c r="H22" s="8">
-        <f>SUM(H2:H21)</f>
+      <c r="H23" s="8">
+        <f>SUM(H2:H22)</f>
         <v/>
       </c>
-      <c r="I22" s="9">
-        <f>SUM(I2:I21)</f>
+      <c r="I23" s="9">
+        <f>SUM(I2:I22)</f>
         <v/>
       </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
@@ -2044,12 +2077,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prior releases (host + 8 features + quality/docs/CI/release infra, through v2.3.0)</t>
+          <t>Prior releases (host + 9 features + quality/docs/CI/release infra, through v2.4.0)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19..10-28</t>
+          <t>2026-06-19..10-29</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2061,15 +2094,15 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n">
-        <v>7.39</v>
+        <v>9.67</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>2788764</v>
+        <v>2995764</v>
       </c>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n">
-        <v>88.34</v>
+        <v>106.39</v>
       </c>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4">
@@ -2078,27 +2111,27 @@
       </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n">
-        <v>955.2</v>
+        <v>1055.3</v>
       </c>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="4" t="n">
-        <v>11.95</v>
+        <v>11</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Phases 1-17 predate DevEconomics tracking (rough estimate); includes the tracked v2.1.0, v2.2.0 and v2.3.0 releases.</t>
+          <t>Phases 1-17 predate DevEconomics tracking (rough estimate); includes the tracked v2.1.0-v2.4.0 releases.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Storage Studio (Space Map)</t>
+          <t>Similar Pictures</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2107,28 +2140,28 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>207000</v>
+        <v>166000</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6.05</v>
+        <v>6.31</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>18.05</v>
+        <v>20.31</v>
       </c>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4">
@@ -2136,18 +2169,18 @@
         <v/>
       </c>
       <c r="N3" s="2" t="n">
-        <v>4.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>100.1</v>
+        <v>106.7</v>
       </c>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="4" t="n">
-        <v>7.92</v>
+        <v>7.64</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Estimate; reconcile ACTUAL via /cost. Phase 1 of Storage Studio (space map); single session.</t>
+          <t>Estimate; reconcile ACTUAL via /cost. Phase 2 of the Storage Studio plan, own plugin; single session.</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2365,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>20 activities (12 LLM / 8 local|remote); ~$18.05 est; ~100.1 min est (~4.1 min measured local compute).</t>
+          <t>21 activities (13 LLM / 8 local|remote); ~$20.31 est; ~106.7 min est (~9.7 min measured local compute).</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2377,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>~9.67 prod KLOC; ~$106.39 est; ~17.6 h est. Foundation portion is a ROUGH pre-tracking estimate.</t>
+          <t>~12.33 prod KLOC; ~$126.7 est; ~19.4 h est. Foundation portion is a ROUGH pre-tracking estimate.</t>
         </is>
       </c>
     </row>

--- a/docs/deveconomics/DigitalSecretary-DevEconomics.xlsx
+++ b/docs/deveconomics/DigitalSecretary-DevEconomics.xlsx
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Check repo + CI after v2.4.0; frame the four design decisions for the owner</t>
+          <t>Locate the project; read Similar Pictures end to end; write the Similar Videos strategy and four decisions for the owner</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Read/Ask</t>
+          <t>Read/Write</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>owner chose: separate plugin, review folder, all match kinds, Windows codecs</t>
+          <t>owner: use the recommended defaults</t>
         </is>
       </c>
     </row>
@@ -1002,44 +1002,46 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Author the pure engine: GrayImage (resize, 8 transforms, sharpness), ImageHasher (pHash DCT + dHash), SimilarityFinder (tiers, star grouping), KeeperRanking</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Baseline quality gate before any change</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>build.ps1 -All</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>22000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>12</v>
+        <v>1.7</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>PASS, 584 unit + 27 QA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1047,12 +1049,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Refactor</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Author I/O edges: Shell thumbnail COM interop + GDI+ fallback, EXIF date/sub-seconds/rotation, cache (gzip), scanner (bounded parallel), ReviewMover (move/recycle/undo), FileBytes</t>
+          <t>ENH-12 kit: move ByteSize/PauseToken/FileBytes/GrayImage/ImageHasher, generic ReviewFolder; UseKit opt-in; golden rule 1 + architecture docs</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1062,7 +1064,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Write/Edit</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1071,20 +1073,24 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3 copies + 4 duplicate test files removed</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1092,41 +1098,39 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Author the review UI: PictureCardControl + SimilarPicturesControl; settings, report, sample set</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Pre-commit gate on the kit commit</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>build.ps1 -NoPrompt</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>16000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -1137,12 +1141,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Refactor</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Rename Orientation -&gt; PictureOrientation (WinForms name clash); add project to sln + tests</t>
+          <t>Kit part 2: FileRecordCache, IncrementalScanner, FileNames, Ranking, SampleScene; Similar Pictures delegates (API unchanged)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1152,7 +1156,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Write/Edit</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1161,20 +1165,24 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3000</v>
+        <v>16000</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>picture tests unchanged and green</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1182,42 +1190,48 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Bugfix</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Compile the feature (0 warnings)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>CA1000 static-on-generic, ScanProgress name clash, three shell-escaping slips on a backslash literal</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>dotnet build</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>6000</v>
+      </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>waste - see journal pitfall</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1225,12 +1239,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Calibrate</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Probe: measure pHash/dHash distances for resize, JPEG, brightness, crop, turns, bursts, unrelated scenes</t>
+          <t>Hand-written Media Foundation interop: Source Reader, Sample, Buffer, Attributes, Sink Writer (no NuGet)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1249,13 +1263,13 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.18</v>
+        <v>0.55</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1264,7 +1278,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>thresholds set from data</t>
+          <t>worked first time</t>
         </is>
       </c>
     </row>
@@ -1274,39 +1288,41 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Calibrate</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Run the probe</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Engine: VideoDecoder/ReaderSession (exact seek, stride, rotation), record + cache, scanner (Live Photos), matcher, keeper ranking, mover, settings, report, sample set</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>dotnet test</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>34000</v>
+      </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.3</v>
+        <v>18</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1322,7 +1338,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Author 12 unit-test files incl. the scan -&gt; group -&gt; move -&gt; rescan -&gt; undo integration test</t>
+          <t>TestVideoWriter (encode MP4s at test time) + Media Foundation round-trip tests</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1341,20 +1357,24 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30000</v>
+        <v>9000</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.15</v>
+        <v>0.35</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>no binary test files</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1362,12 +1382,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Bugfix</t>
+          <t>Calibrate</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fix the int.MaxValue overflow (no pair ever matched), sample capture times, burst bonus on mtime, as-is-only Similar, test inputs</t>
+          <t>Probe: per-frame distances across re-encodes; found codec padding (160x88 decoded as 160x96) and brittle per-frame dHash</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1377,7 +1397,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Write/Edit</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1386,13 +1406,13 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1401,7 +1421,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>found by the tests before release</t>
+          <t>-&gt; crop to aperture; judge dHash on the mean</t>
         </is>
       </c>
     </row>
@@ -1411,48 +1431,42 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Calibrate</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Render two near-matching generated scenes and judge them by eye</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Run the probes</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>dotnet test</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>3000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>they do look alike - test, not code, was wrong</t>
-        </is>
-      </c>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1460,46 +1474,44 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Unit + QA runs</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>Review UI: VideoCardControl (film strip) + SimilarVideosControl</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>dotnet test</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>22000</v>
+      </c>
       <c r="H13" s="4" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>584 unit + 27 QA</t>
-        </is>
-      </c>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1507,44 +1519,46 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>A stray `cat` blocked a shell for 5 minutes until stopped</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>8 unit-test files + the scan -&gt; group -&gt; move -&gt; rescan -&gt; undo pipeline test + kit helper tests</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>bash</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>waste - see journal pitfall</t>
+          <t>all 622 green on the first run</t>
         </is>
       </c>
     </row>
@@ -1559,41 +1573,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>QA test (real plugin, sample set, simulated click) + DocShots hook; fix DocShots cropping the bottom of every view</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Unit + QA runs</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Write/Edit</t>
+          <t>dotnet test</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>9000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>BUG-3</t>
+          <t>622 unit + 30 QA</t>
         </is>
       </c>
     </row>
@@ -1603,39 +1615,41 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Docgen</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Regenerate DocShots screenshots (three times)</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>QA test (real plugin, sample, click) + DocShots hook; card layout fix after looking at the screenshot</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>dotnet run</t>
+          <t>Write/Edit</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>8000</v>
+      </c>
       <c r="H16" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1646,41 +1660,39 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Docgen</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>FEATURE.md, requirement doc (SIM-1..18), user guide, manual section, hubs, README row, Pages card</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Regenerate DocShots screenshots (twice)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>dotnet run</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>22000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>12</v>
+        <v>0.8</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -1691,12 +1703,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Docgen</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18 requirement + 13 traceability rows, SIM id in check_docs regex</t>
+          <t>FEATURE.md, requirement doc (SVD-1..20), user guide, manual section, hubs, README row, Pages card, kit README</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1715,13 +1727,13 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1741,41 +1753,39 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Regenerate requirements/traceability xlsx + HTML user manual; docs check</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>B - Local ($0)</t>
+          <t>20 requirement + 11 traceability rows, SVD id in check_docs regex</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>python + powershell</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>9000</v>
+      </c>
       <c r="H19" s="4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>cleanliness check PASSED</t>
-        </is>
-      </c>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1783,12 +1793,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Docgen</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Full quality gate</t>
+          <t>Regenerate requirements/traceability xlsx + HTML user manual; docs check</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1798,7 +1808,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>build.ps1 -All</t>
+          <t>python + powershell</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1811,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1820,7 +1830,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>PASS, 611 tests, 94.2%</t>
+          <t>cleanliness check PASSED</t>
         </is>
       </c>
     </row>
@@ -1830,46 +1840,44 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CHANGELOG 2.5.0, journal phase 24, DevEconomics, PM trackers</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>A - LLM tokens</t>
+          <t>Full quality gate</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>B - Local ($0)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Write/Edit</t>
+          <t>build.ps1 -All</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>10000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>this release entry</t>
+          <t>PASS, 652 tests, 93.9%</t>
         </is>
       </c>
     </row>
@@ -1879,72 +1887,121 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>CHANGELOG 2.6.0, journal phase 25, DevEconomics, PM trackers, memory note</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>A - LLM tokens</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Write/Edit</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>this release entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Storage report</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>B - Local ($0)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>node storage-report.mjs</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="4" t="n">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>docs/pm/STORAGE.md</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>TOTAL (direct, sum of activities)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="7">
-        <f>SUM(G2:G22)</f>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="7">
+        <f>SUM(G2:G23)</f>
         <v/>
       </c>
-      <c r="H23" s="8">
-        <f>SUM(H2:H22)</f>
+      <c r="H24" s="8">
+        <f>SUM(H2:H23)</f>
         <v/>
       </c>
-      <c r="I23" s="9">
-        <f>SUM(I2:I22)</f>
+      <c r="I24" s="9">
+        <f>SUM(I2:I23)</f>
         <v/>
       </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
@@ -2077,12 +2134,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prior releases (host + 9 features + quality/docs/CI/release infra, through v2.4.0)</t>
+          <t>Prior releases (host + 10 features + quality/docs/CI/release infra, through v2.5.0)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19..10-29</t>
+          <t>2026-06-19..10-30</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2094,15 +2151,15 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n">
-        <v>9.67</v>
+        <v>12.33</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>2995764</v>
+        <v>3161764</v>
       </c>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n">
-        <v>106.39</v>
+        <v>126.7</v>
       </c>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4">
@@ -2111,27 +2168,27 @@
       </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n">
-        <v>1055.3</v>
+        <v>1162</v>
       </c>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="4" t="n">
-        <v>11</v>
+        <v>10.28</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Phases 1-17 predate DevEconomics tracking (rough estimate); includes the tracked v2.1.0-v2.4.0 releases.</t>
+          <t>Phases 1-17 predate DevEconomics tracking (rough estimate); includes the tracked v2.1.0-v2.5.0 releases.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Similar Pictures</t>
+          <t>Similar Videos (+ shared helper kit)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2140,28 +2197,28 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>166000</v>
+        <v>231000</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6.31</v>
+        <v>8.82</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>20.31</v>
+        <v>30.82</v>
       </c>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4">
@@ -2169,18 +2226,18 @@
         <v/>
       </c>
       <c r="N3" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>106.7</v>
+        <v>130.3</v>
       </c>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="4" t="n">
-        <v>7.64</v>
+        <v>11.85</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Estimate; reconcile ACTUAL via /cost. Phase 2 of the Storage Studio plan, own plugin; single session.</t>
+          <t>Estimate; reconcile ACTUAL via /cost. Phase 3 of the Storage Studio plan, own plugin, plus the ENH-12 helper kit; single session.</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2422,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>21 activities (13 LLM / 8 local|remote); ~$20.31 est; ~106.7 min est (~9.7 min measured local compute).</t>
+          <t>22 activities (14 LLM / 8 local|remote); ~$30.82 est; ~130.3 min est (~7.3 min measured local compute).</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2434,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>~12.33 prod KLOC; ~$126.7 est; ~19.4 h est. Foundation portion is a ROUGH pre-tracking estimate.</t>
+          <t>~14.93 prod KLOC; ~$157.52 est; ~21.5 h est. Foundation portion is a ROUGH pre-tracking estimate.</t>
         </is>
       </c>
     </row>
